--- a/samples/tracking01/tracking04.xlsx
+++ b/samples/tracking01/tracking04.xlsx
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>frame_index</t>
+          <t>frame_index_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
